--- a/i18n/fr.xlsx
+++ b/i18n/fr.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Birds" sheetId="1" r:id="rId1"/>
@@ -4804,7 +4804,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">3 </t>
     </r>
@@ -4823,7 +4824,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 3[point]; 4 </t>
     </r>
@@ -4842,7 +4844,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">: 5[point]; 5 </t>
     </r>
@@ -4861,7 +4864,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t>: 8[point]</t>
     </r>
@@ -4893,7 +4897,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve">1 </t>
     </r>
@@ -4912,7 +4917,8 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
       <t xml:space="preserve"> = [bowl] [cavity] [ground] [platform]; 1 série: 3[point]; 2+ série: 8[point]</t>
     </r>
@@ -4954,9 +4960,6 @@
     <t>Les oiseaux qui n'ont pas de limite d'œufs ne comptent pas pour cette carte.</t>
   </si>
   <si>
-    <t>5 à 6 oiseaux : 4[point]; 7+ oiseaux : 7[point]</t>
-  </si>
-  <si>
     <t>Endangered Species Protector</t>
   </si>
   <si>
@@ -4981,9 +4984,6 @@
     <t>Vous pouvez comptez chaque nid étoile comme un autre type de nid, ou comme un cinquième type de nid.</t>
   </si>
   <si>
-    <t>2 à 3 types : 3[point]; 4 types : 5[point]; 5 types : 8[point]</t>
-  </si>
-  <si>
     <t>Forest Ranger</t>
   </si>
   <si>
@@ -4996,9 +4996,6 @@
     <t>Le score de chaque oiseaux doit être suppérieur au précédent en allant de gauche à droite ou de droite à gauche.</t>
   </si>
   <si>
-    <t>3 oiseaux successifs : 3[point]; 4 oiseaux successifs : 5[point]; 5 oiseaux successifs : 8[point]</t>
-  </si>
-  <si>
     <t>Grassland Population Monitor</t>
   </si>
   <si>
@@ -5026,9 +5023,6 @@
     <t>Jetons [fish] et [rodent] stockés sur vos oiseaux.</t>
   </si>
   <si>
-    <t>2 à 3 jetons stockés : 3[point]; 4+ jetons stockés : 6[point]</t>
-  </si>
-  <si>
     <t>(13% des oiseaux peuvent stocker de la nourriture)</t>
   </si>
   <si>
@@ -5044,9 +5038,6 @@
     <t>Vous pouvez comptez les oiseaux qui n'ont pas de limite d'œufs.</t>
   </si>
   <si>
-    <t>5 à 7 oiseaux : 3[point]; 8+ oiseaux : 7[point]</t>
-  </si>
-  <si>
     <t>(44% des cartes)</t>
   </si>
   <si>
@@ -5077,9 +5068,6 @@
     <t>Nourriture dans votre réserve à la fin de la partie</t>
   </si>
   <si>
-    <t>4 à 6 jetons nourriture : 4[point]; 7+ jetons nourriture : 7[point]</t>
-  </si>
-  <si>
     <t>[automa] Avid Asian Avian Admirer</t>
   </si>
   <si>
@@ -5098,142 +5086,7 @@
     <t>Explanatory Text</t>
   </si>
   <si>
-    <t>Bird in Forest</t>
-  </si>
-  <si>
-    <t>Bird in Grassland</t>
-  </si>
-  <si>
-    <t>Bird in Wetland</t>
-  </si>
-  <si>
-    <t>Egg in Forest</t>
-  </si>
-  <si>
-    <t>Egg in Grassland</t>
-  </si>
-  <si>
-    <t>Egg in Wetland</t>
-  </si>
-  <si>
-    <t>Cavity Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Bowl Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Ground Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Platform Nest Bird with Egg</t>
-  </si>
-  <si>
-    <t>Egg in Cavity Nest</t>
-  </si>
-  <si>
-    <t>Egg in Bowl Nest</t>
-  </si>
-  <si>
-    <t>Egg in Ground Nest</t>
-  </si>
-  <si>
-    <t>Egg in Platform Nest</t>
-  </si>
-  <si>
-    <t>Sets of Eggs in 3 Habitats</t>
-  </si>
-  <si>
-    <t>Total Bird</t>
-  </si>
-  <si>
-    <t>Food in Supply</t>
-  </si>
-  <si>
     <t>Birds Cards in Hand</t>
-  </si>
-  <si>
-    <t>Birds Worth over 4 Points</t>
-  </si>
-  <si>
-    <t>Birds with No Eggs</t>
-  </si>
-  <si>
-    <t>Birds in 1 Row</t>
-  </si>
-  <si>
-    <t>Filled Columns</t>
-  </si>
-  <si>
-    <t>Brown Powers</t>
-  </si>
-  <si>
-    <t>White &amp; No Powers</t>
-  </si>
-  <si>
-    <t>Birds with Tucked Cards</t>
-  </si>
-  <si>
-    <t>Food Cost of Played Birds</t>
-  </si>
-  <si>
-    <t>Invertebrate in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Fruit + Seed in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>Rodent + Fish in Food Cost of Your Birds</t>
-  </si>
-  <si>
-    <t>No Goal</t>
-  </si>
-  <si>
-    <t>Beak Pointing Left</t>
-  </si>
-  <si>
-    <t>Beak Pointing Right</t>
-  </si>
-  <si>
-    <t>Cubes on "Play a Bird"</t>
-  </si>
-  <si>
-    <t>Birds Worth Less than or Equal to 3 Points</t>
-  </si>
-  <si>
-    <t>Pairs of Matching Symbols</t>
-  </si>
-  <si>
-    <t>Nest Symbols</t>
-  </si>
-  <si>
-    <t>Food Symbols</t>
-  </si>
-  <si>
-    <t>Not on Edge of Map</t>
-  </si>
-  <si>
-    <t>On Edge of Map</t>
-  </si>
-  <si>
-    <t>Tokens in Any One Horizontal Row</t>
-  </si>
-  <si>
-    <t>Horizontal Rows with at Least One of Your Tokens</t>
-  </si>
-  <si>
-    <t>Fewest Tokens on Bonus Spaces</t>
-  </si>
-  <si>
-    <t>In Forest</t>
-  </si>
-  <si>
-    <t>In Grassland</t>
-  </si>
-  <si>
-    <t>In Wetland</t>
-  </si>
-  <si>
-    <t>Total Duet Tokens</t>
   </si>
   <si>
     <t>Translated</t>
@@ -6388,6 +6241,159 @@
   <si>
     <t>Flavor text</t>
   </si>
+  <si>
+    <t>5 à 6 oiseaux: 4[point]; 7+ oiseaux: 7[point]</t>
+  </si>
+  <si>
+    <t>2 à 3 types: 3[point]; 4 types: 5[point]; 5 types: 8[point]</t>
+  </si>
+  <si>
+    <t>3 oiseaux successifs: 3[point]; 4 oiseaux successifs: 5[point]; 5 oiseaux successifs: 8[point]</t>
+  </si>
+  <si>
+    <t>2 à 3 jetons stockés: 3[point]; 4+ jetons stockés: 6[point]</t>
+  </si>
+  <si>
+    <t>4 à 6 jetons nourriture: 4[point]; 7+ jetons nourriture: 7[point]</t>
+  </si>
+  <si>
+    <t>2 à 3 types: 3[point]; 4 types: 5[point]; 5 type: 8[point]</t>
+  </si>
+  <si>
+    <t>Birds in Forest</t>
+  </si>
+  <si>
+    <t>Birds in Grassland</t>
+  </si>
+  <si>
+    <t>Birds in Wetland</t>
+  </si>
+  <si>
+    <t>Eggs in Forest</t>
+  </si>
+  <si>
+    <t>Eggs in Grassland</t>
+  </si>
+  <si>
+    <t>Eggs in Wetland</t>
+  </si>
+  <si>
+    <t>Cavity nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Bowl nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Ground nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Platform nest birds with eggs</t>
+  </si>
+  <si>
+    <t>Eggs in Cavity Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Bowl Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Ground Nest</t>
+  </si>
+  <si>
+    <t>Eggs in Platform Nest</t>
+  </si>
+  <si>
+    <t>Sets of eggs in 3 habitats</t>
+  </si>
+  <si>
+    <t>Total birds</t>
+  </si>
+  <si>
+    <t>Food in personal supply</t>
+  </si>
+  <si>
+    <t>Birds worth over 4 points</t>
+  </si>
+  <si>
+    <t>Birds with no eggs</t>
+  </si>
+  <si>
+    <t>Birds in one row</t>
+  </si>
+  <si>
+    <t>Filled columns</t>
+  </si>
+  <si>
+    <t>Brown powers</t>
+  </si>
+  <si>
+    <t>White &amp; no powers</t>
+  </si>
+  <si>
+    <t>Birds with tucked cards</t>
+  </si>
+  <si>
+    <t>Food cost of played birds</t>
+  </si>
+  <si>
+    <t>Invertebrate in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Fruit + Seed in food cost of your birds</t>
+  </si>
+  <si>
+    <t>Rodent + Fish in food cost of your birds</t>
+  </si>
+  <si>
+    <t>No goal</t>
+  </si>
+  <si>
+    <t>Beak pointing left</t>
+  </si>
+  <si>
+    <t>Beak pointing right</t>
+  </si>
+  <si>
+    <t>Cubes on "play a bird"</t>
+  </si>
+  <si>
+    <t>Birds worth less than or equal to 3 points</t>
+  </si>
+  <si>
+    <t>Duet tokens on pairs of matching symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on nest symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens on food symbols</t>
+  </si>
+  <si>
+    <t>Duet tokens not on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens on edge of map</t>
+  </si>
+  <si>
+    <t>Duet tokens in any one horizontal row</t>
+  </si>
+  <si>
+    <t>Horizontal rows with at least 1 of your duet tokens</t>
+  </si>
+  <si>
+    <t>Fewest duet tokens on bonus spaces</t>
+  </si>
+  <si>
+    <t>Duet tokens in Forest</t>
+  </si>
+  <si>
+    <t>Duet tokens in Grassland</t>
+  </si>
+  <si>
+    <t>Duet tokens in Wetland</t>
+  </si>
+  <si>
+    <t>Total duet tokens</t>
+  </si>
 </sst>
 </file>
 
@@ -6396,7 +6402,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;PRAWDA&quot;;&quot;PRAWDA&quot;;&quot;FAŁSZ&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -6415,7 +6421,8 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <b/>
@@ -6451,13 +6458,21 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -6497,7 +6512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6549,6 +6564,8 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6834,7 +6851,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>2054</v>
+        <v>2003</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -6869,10 +6886,10 @@
         <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
@@ -6896,10 +6913,10 @@
         <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1936</v>
+        <v>1885</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>2027</v>
+        <v>1976</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
@@ -6929,7 +6946,7 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>1937</v>
+        <v>1886</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
@@ -7068,7 +7085,7 @@
         <v>43</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1933</v>
+        <v>1882</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
@@ -7510,11 +7527,11 @@
         <v>112</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>1938</v>
+        <v>1887</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>2027</v>
+        <v>1976</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
@@ -7573,7 +7590,7 @@
         <v>119</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>2037</v>
+        <v>1986</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
@@ -7603,7 +7620,7 @@
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -7766,7 +7783,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>1925</v>
+        <v>1874</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>146</v>
@@ -8015,7 +8032,7 @@
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>18</v>
@@ -8043,10 +8060,10 @@
         <v>182</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
@@ -8289,11 +8306,11 @@
         <v>216</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>1939</v>
+        <v>1888</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="s">
-        <v>2027</v>
+        <v>1976</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -8345,11 +8362,11 @@
         <v>223</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>1939</v>
+        <v>1888</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4" t="s">
-        <v>2027</v>
+        <v>1976</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>18</v>
@@ -8572,10 +8589,10 @@
         <v>252</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1940</v>
+        <v>1889</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
@@ -8864,7 +8881,7 @@
         <v>123</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -8941,10 +8958,10 @@
         <v>297</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="s">
@@ -9258,7 +9275,7 @@
       </c>
       <c r="G86" s="6"/>
       <c r="H86" s="6" t="s">
-        <v>1937</v>
+        <v>1886</v>
       </c>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
@@ -9313,7 +9330,7 @@
         <v>352</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>2038</v>
+        <v>1987</v>
       </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
@@ -9340,7 +9357,7 @@
         <v>123</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3" t="s">
@@ -9646,7 +9663,7 @@
         <v>395</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
@@ -9698,7 +9715,7 @@
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I102" s="3"/>
       <c r="J102" s="3" t="s">
@@ -9756,7 +9773,7 @@
         <v>410</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>2037</v>
+        <v>1986</v>
       </c>
       <c r="I104" s="3"/>
       <c r="J104" s="3"/>
@@ -9792,7 +9809,7 @@
         <v>106</v>
       </c>
       <c r="B106" t="s">
-        <v>1926</v>
+        <v>1875</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>415</v>
@@ -10426,7 +10443,7 @@
       </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5" t="s">
-        <v>2038</v>
+        <v>1987</v>
       </c>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
@@ -10532,7 +10549,7 @@
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
@@ -10611,7 +10628,7 @@
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
@@ -10705,7 +10722,7 @@
         <v>139</v>
       </c>
       <c r="B139" t="s">
-        <v>1928</v>
+        <v>1877</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>541</v>
@@ -11096,7 +11113,7 @@
         <v>595</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
@@ -11176,11 +11193,11 @@
         <v>606</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>1940</v>
+        <v>1889</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
@@ -11319,7 +11336,7 @@
       </c>
       <c r="G161" s="4"/>
       <c r="H161" s="4" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
@@ -11404,7 +11421,7 @@
         <v>635</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
@@ -11580,7 +11597,7 @@
       </c>
       <c r="G170" s="4"/>
       <c r="H170" s="4" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
@@ -11606,10 +11623,10 @@
         <v>659</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>1940</v>
+        <v>1889</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
@@ -11712,7 +11729,7 @@
         <v>673</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>1941</v>
+        <v>1890</v>
       </c>
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
@@ -11785,7 +11802,7 @@
         <v>84</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>1708</v>
+        <v>1657</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>201</v>
@@ -11806,7 +11823,7 @@
         <v>683</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>1929</v>
+        <v>1878</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>13</v>
@@ -12340,10 +12357,10 @@
         <v>749</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I198" s="3" t="s">
         <v>18</v>
@@ -12398,11 +12415,11 @@
         <v>755</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>1940</v>
+        <v>1889</v>
       </c>
       <c r="G200" s="7"/>
       <c r="H200" s="7" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I200" s="3" t="s">
         <v>18</v>
@@ -12465,7 +12482,7 @@
         <v>395</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I202" s="3" t="s">
         <v>18</v>
@@ -12493,10 +12510,10 @@
         <v>764</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I203" s="3" t="s">
         <v>18</v>
@@ -12726,7 +12743,7 @@
         <v>395</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I211" s="3" t="s">
         <v>18</v>
@@ -12872,7 +12889,7 @@
         <v>403</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I216" s="3"/>
       <c r="J216" s="3" t="s">
@@ -13012,7 +13029,7 @@
         <v>825</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>2038</v>
+        <v>1987</v>
       </c>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
@@ -13122,7 +13139,7 @@
         <v>123</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
@@ -13283,10 +13300,10 @@
         <v>858</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>1934</v>
+        <v>1883</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I231" s="3"/>
       <c r="J231" s="3"/>
@@ -13421,7 +13438,7 @@
       </c>
       <c r="G236" s="7"/>
       <c r="H236" s="7" t="s">
-        <v>2028</v>
+        <v>1977</v>
       </c>
       <c r="I236" s="3"/>
       <c r="J236" s="3"/>
@@ -13672,10 +13689,10 @@
         <v>903</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1940</v>
+        <v>1889</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>1935</v>
+        <v>1884</v>
       </c>
       <c r="I245" s="3" t="s">
         <v>18</v>
@@ -13706,7 +13723,7 @@
         <v>123</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I246" s="3" t="s">
         <v>18</v>
@@ -14045,11 +14062,11 @@
         <v>943</v>
       </c>
       <c r="F258" s="8" t="s">
-        <v>1939</v>
+        <v>1888</v>
       </c>
       <c r="G258" s="8"/>
       <c r="H258" s="8" t="s">
-        <v>2027</v>
+        <v>1976</v>
       </c>
       <c r="I258" s="3" t="s">
         <v>18</v>
@@ -14080,7 +14097,7 @@
         <v>123</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>2053</v>
+        <v>2002</v>
       </c>
       <c r="I259" s="3"/>
       <c r="J259" s="3"/>
@@ -14191,7 +14208,7 @@
         <v>958</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1942</v>
+        <v>1891</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>959</v>
@@ -14220,7 +14237,7 @@
         <v>958</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1943</v>
+        <v>1892</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>963</v>
@@ -14246,7 +14263,7 @@
         <v>958</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1944</v>
+        <v>1893</v>
       </c>
       <c r="F265" s="2" t="s">
         <v>966</v>
@@ -14272,7 +14289,7 @@
         <v>958</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1945</v>
+        <v>1894</v>
       </c>
       <c r="F266" s="2" t="s">
         <v>969</v>
@@ -14303,7 +14320,7 @@
         <v>958</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1946</v>
+        <v>1895</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>973</v>
@@ -14329,10 +14346,10 @@
         <v>958</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1947</v>
+        <v>1896</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>2039</v>
+        <v>1988</v>
       </c>
       <c r="I268" s="3"/>
       <c r="J268" s="3" t="s">
@@ -14355,7 +14372,7 @@
         <v>958</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1948</v>
+        <v>1897</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>978</v>
@@ -14381,7 +14398,7 @@
         <v>958</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1949</v>
+        <v>1898</v>
       </c>
       <c r="F270" s="2" t="s">
         <v>981</v>
@@ -14407,13 +14424,13 @@
         <v>958</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>1950</v>
+        <v>1899</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>984</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>2029</v>
+        <v>1978</v>
       </c>
       <c r="I271" s="3"/>
       <c r="J271" s="3" t="s">
@@ -14436,7 +14453,7 @@
         <v>958</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>1951</v>
+        <v>1900</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>987</v>
@@ -14462,7 +14479,7 @@
         <v>958</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>1952</v>
+        <v>1901</v>
       </c>
       <c r="F273" s="2" t="s">
         <v>990</v>
@@ -14549,7 +14566,7 @@
         <v>958</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>1953</v>
+        <v>1902</v>
       </c>
       <c r="F276" s="2" t="s">
         <v>1003</v>
@@ -14573,7 +14590,7 @@
         <v>958</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>1954</v>
+        <v>1903</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>1006</v>
@@ -14626,11 +14643,11 @@
         <v>1013</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>1955</v>
+        <v>1904</v>
       </c>
       <c r="G279" s="4"/>
       <c r="H279" s="4" t="s">
-        <v>1956</v>
+        <v>1905</v>
       </c>
       <c r="I279" s="3"/>
       <c r="J279" s="3"/>
@@ -14651,7 +14668,7 @@
         <v>958</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>1957</v>
+        <v>1906</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>1016</v>
@@ -14678,7 +14695,7 @@
         <v>958</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1958</v>
+        <v>1907</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>1020</v>
@@ -14704,7 +14721,7 @@
         <v>958</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1959</v>
+        <v>1908</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>1023</v>
@@ -14728,7 +14745,7 @@
         <v>958</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1960</v>
+        <v>1909</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>1026</v>
@@ -14754,7 +14771,7 @@
         <v>958</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>1961</v>
+        <v>1910</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>1029</v>
@@ -14778,7 +14795,7 @@
         <v>958</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>1962</v>
+        <v>1911</v>
       </c>
       <c r="F285" s="2" t="s">
         <v>1032</v>
@@ -14806,7 +14823,7 @@
         <v>958</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1963</v>
+        <v>1912</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>1035</v>
@@ -14835,7 +14852,7 @@
         <v>958</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1964</v>
+        <v>1913</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>1039</v>
@@ -14859,7 +14876,7 @@
         <v>958</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>1965</v>
+        <v>1914</v>
       </c>
       <c r="F288" s="7" t="s">
         <v>1042</v>
@@ -14887,13 +14904,13 @@
         <v>958</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>1966</v>
+        <v>1915</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>2040</v>
+        <v>1989</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>2047</v>
+        <v>1996</v>
       </c>
       <c r="I289" s="3"/>
       <c r="J289" s="3"/>
@@ -14916,7 +14933,7 @@
         <v>958</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>1967</v>
+        <v>1916</v>
       </c>
       <c r="F290" s="2" t="s">
         <v>1047</v>
@@ -14940,7 +14957,7 @@
         <v>958</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>1968</v>
+        <v>1917</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>1050</v>
@@ -14964,7 +14981,7 @@
         <v>958</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>1969</v>
+        <v>1918</v>
       </c>
       <c r="F292" s="2" t="s">
         <v>1053</v>
@@ -15019,7 +15036,7 @@
         <v>958</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>1970</v>
+        <v>1919</v>
       </c>
       <c r="F294" s="7" t="s">
         <v>1060</v>
@@ -15047,13 +15064,13 @@
         <v>958</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>1971</v>
+        <v>1920</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>2041</v>
+        <v>1990</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>2048</v>
+        <v>1997</v>
       </c>
       <c r="I295" s="3"/>
       <c r="J295" s="3"/>
@@ -15076,10 +15093,10 @@
         <v>958</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>1972</v>
+        <v>1921</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>2052</v>
+        <v>2001</v>
       </c>
       <c r="I296" s="3"/>
       <c r="J296" s="3"/>
@@ -15102,7 +15119,7 @@
         <v>958</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1973</v>
+        <v>1922</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>1067</v>
@@ -15117,7 +15134,7 @@
         <v>298</v>
       </c>
       <c r="B298" s="19" t="s">
-        <v>1931</v>
+        <v>1880</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>1069</v>
@@ -15150,7 +15167,7 @@
         <v>958</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>1974</v>
+        <v>1923</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>1073</v>
@@ -15179,7 +15196,7 @@
         <v>958</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>1975</v>
+        <v>1924</v>
       </c>
       <c r="F300" s="2" t="s">
         <v>1077</v>
@@ -15231,7 +15248,7 @@
         <v>958</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1976</v>
+        <v>1925</v>
       </c>
       <c r="F302" s="2" t="s">
         <v>1084</v>
@@ -15255,7 +15272,7 @@
         <v>958</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1977</v>
+        <v>1926</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>1087</v>
@@ -15285,7 +15302,7 @@
         <v>1091</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>2023</v>
+        <v>1972</v>
       </c>
       <c r="I304" s="3"/>
       <c r="J304" s="3"/>
@@ -15306,7 +15323,7 @@
         <v>958</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1978</v>
+        <v>1927</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>1094</v>
@@ -15332,7 +15349,7 @@
         <v>958</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1979</v>
+        <v>1928</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>1097</v>
@@ -15383,13 +15400,13 @@
         <v>958</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1980</v>
+        <v>1929</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>2049</v>
+        <v>1998</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>2048</v>
+        <v>1997</v>
       </c>
       <c r="I308" s="3"/>
       <c r="J308" s="3"/>
@@ -15410,7 +15427,7 @@
         <v>958</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1981</v>
+        <v>1930</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>1107</v>
@@ -15438,7 +15455,7 @@
         <v>958</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1982</v>
+        <v>1931</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>1110</v>
@@ -15485,7 +15502,7 @@
         <v>312</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1927</v>
+        <v>1876</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>1116</v>
@@ -15494,7 +15511,7 @@
         <v>958</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>1983</v>
+        <v>1932</v>
       </c>
       <c r="F312" s="2" t="s">
         <v>1117</v>
@@ -15518,7 +15535,7 @@
         <v>958</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1984</v>
+        <v>1933</v>
       </c>
       <c r="F313" s="2" t="s">
         <v>1120</v>
@@ -15545,7 +15562,7 @@
         <v>958</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1985</v>
+        <v>1934</v>
       </c>
       <c r="F314" s="2" t="s">
         <v>1124</v>
@@ -15569,14 +15586,14 @@
         <v>958</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>1986</v>
+        <v>1935</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="G315" s="4"/>
       <c r="H315" s="4" t="s">
-        <v>2029</v>
+        <v>1978</v>
       </c>
       <c r="I315" s="3" t="s">
         <v>18</v>
@@ -15599,13 +15616,13 @@
         <v>958</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1987</v>
+        <v>1936</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>1130</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>2024</v>
+        <v>1973</v>
       </c>
       <c r="I316" s="3"/>
       <c r="J316" s="3" t="s">
@@ -15628,7 +15645,7 @@
         <v>958</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1988</v>
+        <v>1937</v>
       </c>
       <c r="F317" s="2" t="s">
         <v>1133</v>
@@ -15678,7 +15695,7 @@
         <v>958</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1989</v>
+        <v>1938</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>1110</v>
@@ -15708,13 +15725,13 @@
         <v>958</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1990</v>
+        <v>1939</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>1142</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>2030</v>
+        <v>1979</v>
       </c>
       <c r="I320" s="3" t="s">
         <v>18</v>
@@ -15737,7 +15754,7 @@
         <v>958</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1991</v>
+        <v>1940</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>1145</v>
@@ -15761,7 +15778,7 @@
         <v>958</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1992</v>
+        <v>1941</v>
       </c>
       <c r="F322" s="2" t="s">
         <v>1148</v>
@@ -15787,10 +15804,10 @@
         <v>958</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1993</v>
+        <v>1942</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>2042</v>
+        <v>1991</v>
       </c>
       <c r="I323" s="3"/>
       <c r="J323" s="3"/>
@@ -15811,7 +15828,7 @@
         <v>958</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1994</v>
+        <v>1943</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>1047</v>
@@ -15863,7 +15880,7 @@
         <v>958</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1995</v>
+        <v>1944</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>1159</v>
@@ -15892,7 +15909,7 @@
         <v>1162</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>2025</v>
+        <v>1974</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>1163</v>
@@ -15942,7 +15959,7 @@
         <v>958</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1996</v>
+        <v>1945</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>1170</v>
@@ -15970,7 +15987,7 @@
         <v>958</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>1173</v>
@@ -16001,7 +16018,7 @@
         <v>958</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1998</v>
+        <v>1947</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>1177</v>
@@ -16029,7 +16046,7 @@
         <v>958</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1999</v>
+        <v>1948</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>1180</v>
@@ -16055,7 +16072,7 @@
         <v>958</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>2000</v>
+        <v>1949</v>
       </c>
       <c r="F333" s="2" t="s">
         <v>1183</v>
@@ -16079,7 +16096,7 @@
         <v>958</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>2001</v>
+        <v>1950</v>
       </c>
       <c r="F334" s="2" t="s">
         <v>1032</v>
@@ -16105,13 +16122,13 @@
         <v>958</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>2002</v>
+        <v>1951</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>1188</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>2029</v>
+        <v>1978</v>
       </c>
       <c r="I335" s="3"/>
       <c r="J335" s="3"/>
@@ -16132,7 +16149,7 @@
         <v>958</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>2003</v>
+        <v>1952</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>1191</v>
@@ -16158,7 +16175,7 @@
         <v>958</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>2004</v>
+        <v>1953</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>1194</v>
@@ -16184,7 +16201,7 @@
         <v>958</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>2005</v>
+        <v>1954</v>
       </c>
       <c r="F338" s="2" t="s">
         <v>1197</v>
@@ -16212,10 +16229,10 @@
         <v>958</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>2006</v>
+        <v>1955</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>2043</v>
+        <v>1992</v>
       </c>
       <c r="H339" s="2" t="s">
         <v>1200</v>
@@ -16239,7 +16256,7 @@
         <v>958</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>2007</v>
+        <v>1956</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>1203</v>
@@ -16267,7 +16284,7 @@
         <v>958</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>2008</v>
+        <v>1957</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>1206</v>
@@ -16291,7 +16308,7 @@
         <v>958</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>2009</v>
+        <v>1958</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>1209</v>
@@ -16318,10 +16335,10 @@
         <v>958</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>2010</v>
+        <v>1959</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>2026</v>
+        <v>1975</v>
       </c>
       <c r="I343" s="3"/>
       <c r="J343" s="3"/>
@@ -16344,7 +16361,7 @@
         <v>958</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>2011</v>
+        <v>1960</v>
       </c>
       <c r="F344" s="7" t="s">
         <v>1215</v>
@@ -16372,7 +16389,7 @@
         <v>958</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>2012</v>
+        <v>1961</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>1218</v>
@@ -16399,7 +16416,7 @@
         <v>958</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>2013</v>
+        <v>1962</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>1222</v>
@@ -16423,7 +16440,7 @@
         <v>958</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>2014</v>
+        <v>1963</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>1225</v>
@@ -16451,13 +16468,13 @@
         <v>958</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>2015</v>
+        <v>1964</v>
       </c>
       <c r="F348" s="2" t="s">
         <v>1228</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>2044</v>
+        <v>1993</v>
       </c>
       <c r="I348" s="3"/>
       <c r="J348" s="3"/>
@@ -16514,7 +16531,7 @@
       </c>
       <c r="G350" s="7"/>
       <c r="H350" s="7" t="s">
-        <v>2044</v>
+        <v>1993</v>
       </c>
       <c r="I350" s="3"/>
       <c r="J350" s="3"/>
@@ -16535,7 +16552,7 @@
         <v>958</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>2016</v>
+        <v>1965</v>
       </c>
       <c r="F351" s="2" t="s">
         <v>1239</v>
@@ -16564,7 +16581,7 @@
         <v>958</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>2017</v>
+        <v>1966</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>1243</v>
@@ -16588,7 +16605,7 @@
         <v>958</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>2018</v>
+        <v>1967</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>1246</v>
@@ -16619,7 +16636,7 @@
         <v>958</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>2019</v>
+        <v>1968</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>1249</v>
@@ -16647,7 +16664,7 @@
         <v>958</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>2020</v>
+        <v>1969</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>1252</v>
@@ -16678,14 +16695,14 @@
         <v>958</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>2021</v>
+        <v>1970</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>984</v>
       </c>
       <c r="G356" s="4"/>
       <c r="H356" s="4" t="s">
-        <v>2029</v>
+        <v>1978</v>
       </c>
       <c r="I356" s="3"/>
       <c r="J356" s="3"/>
@@ -16706,7 +16723,7 @@
         <v>958</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>2022</v>
+        <v>1971</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>1258</v>
@@ -16735,10 +16752,10 @@
         <v>1262</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>1714</v>
+        <v>1663</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>1709</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="359" spans="1:12" ht="150">
@@ -16755,13 +16772,13 @@
         <v>1262</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>1715</v>
+        <v>1664</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>1710</v>
+        <v>1659</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>2031</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="360" spans="1:12" ht="30">
@@ -16778,10 +16795,10 @@
         <v>1262</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>1716</v>
+        <v>1665</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>1711</v>
+        <v>1660</v>
       </c>
       <c r="L360" s="1" t="s">
         <v>18</v>
@@ -16801,10 +16818,10 @@
         <v>1262</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>1717</v>
+        <v>1666</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>1712</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="362" spans="1:12" ht="45">
@@ -16821,10 +16838,10 @@
         <v>1262</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>1718</v>
+        <v>1667</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>1720</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="363" spans="1:12" ht="75">
@@ -16841,13 +16858,13 @@
         <v>1262</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1721</v>
+        <v>1670</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>1722</v>
+        <v>1671</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>1723</v>
+        <v>1672</v>
       </c>
       <c r="L363" s="1" t="s">
         <v>18</v>
@@ -16867,10 +16884,10 @@
         <v>1262</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>1719</v>
+        <v>1668</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>1713</v>
+        <v>1662</v>
       </c>
       <c r="L364" s="1" t="s">
         <v>18</v>
@@ -16890,13 +16907,13 @@
         <v>1262</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>1724</v>
+        <v>1673</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>1725</v>
+        <v>1674</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>1726</v>
+        <v>1675</v>
       </c>
       <c r="J365" s="1" t="s">
         <v>18</v>
@@ -16919,13 +16936,13 @@
         <v>1262</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>1727</v>
+        <v>1676</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>1728</v>
+        <v>1677</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>1729</v>
+        <v>1678</v>
       </c>
       <c r="L366" s="1" t="s">
         <v>18</v>
@@ -16945,13 +16962,13 @@
         <v>1262</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>1730</v>
+        <v>1679</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>1731</v>
+        <v>1680</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>1732</v>
+        <v>1681</v>
       </c>
       <c r="L367" s="1" t="s">
         <v>18</v>
@@ -16971,13 +16988,13 @@
         <v>1262</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>1733</v>
+        <v>1682</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>1734</v>
+        <v>1683</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>1735</v>
+        <v>1684</v>
       </c>
       <c r="J368" s="1" t="s">
         <v>18</v>
@@ -16997,13 +17014,13 @@
         <v>1262</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>1736</v>
+        <v>1685</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>1737</v>
+        <v>1686</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>2045</v>
+        <v>1994</v>
       </c>
       <c r="L369" s="1" t="s">
         <v>18</v>
@@ -17023,13 +17040,13 @@
         <v>1262</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>1738</v>
+        <v>1687</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>1739</v>
+        <v>1688</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>1740</v>
+        <v>1689</v>
       </c>
       <c r="L370" s="1" t="s">
         <v>18</v>
@@ -17049,10 +17066,10 @@
         <v>1262</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>1741</v>
+        <v>1690</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>1742</v>
+        <v>1691</v>
       </c>
       <c r="J371" s="1" t="s">
         <v>18</v>
@@ -17072,13 +17089,13 @@
         <v>1262</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>1743</v>
+        <v>1692</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>1744</v>
+        <v>1693</v>
       </c>
       <c r="H372" s="2" t="s">
-        <v>2046</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="373" spans="1:12" ht="45">
@@ -17095,10 +17112,10 @@
         <v>1262</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>1745</v>
+        <v>1694</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>1746</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="374" spans="1:12" ht="90">
@@ -17115,13 +17132,13 @@
         <v>1262</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>1747</v>
+        <v>1696</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>1748</v>
+        <v>1697</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>2033</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="375" spans="1:12" ht="45">
@@ -17138,13 +17155,13 @@
         <v>1262</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>1749</v>
+        <v>1698</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>1750</v>
+        <v>1699</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>1751</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="376" spans="1:12" ht="60">
@@ -17161,13 +17178,13 @@
         <v>1262</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>1752</v>
+        <v>1701</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>603</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>1922</v>
+        <v>1871</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>18</v>
@@ -17190,13 +17207,13 @@
         <v>1262</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>1753</v>
+        <v>1702</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>1754</v>
+        <v>1703</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>2050</v>
+        <v>1999</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>18</v>
@@ -17216,13 +17233,13 @@
         <v>1262</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>1755</v>
+        <v>1704</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>1756</v>
+        <v>1705</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>1757</v>
+        <v>1706</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>18</v>
@@ -17242,10 +17259,10 @@
         <v>1262</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>1758</v>
+        <v>1707</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>1759</v>
+        <v>1708</v>
       </c>
       <c r="J379" s="1" t="s">
         <v>18</v>
@@ -17265,13 +17282,13 @@
         <v>1262</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>1760</v>
+        <v>1709</v>
       </c>
       <c r="F380" s="2" t="s">
-        <v>1761</v>
+        <v>1710</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>1762</v>
+        <v>1711</v>
       </c>
       <c r="J380" s="1" t="s">
         <v>18</v>
@@ -17291,10 +17308,10 @@
         <v>1262</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>1763</v>
+        <v>1712</v>
       </c>
       <c r="F381" s="2" t="s">
-        <v>1764</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="382" spans="1:12" ht="375">
@@ -17311,13 +17328,13 @@
         <v>1262</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>1765</v>
+        <v>1714</v>
       </c>
       <c r="F382" s="2" t="s">
-        <v>1766</v>
+        <v>1715</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>1767</v>
+        <v>1716</v>
       </c>
       <c r="J382" s="1" t="s">
         <v>18</v>
@@ -17337,13 +17354,13 @@
         <v>1262</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>1768</v>
+        <v>1717</v>
       </c>
       <c r="F383" s="2" t="s">
-        <v>1769</v>
+        <v>1718</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>1770</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="384" spans="1:12" ht="45">
@@ -17360,13 +17377,13 @@
         <v>1262</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>1771</v>
+        <v>1720</v>
       </c>
       <c r="F384" s="2" t="s">
-        <v>1772</v>
+        <v>1721</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>1773</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="385" spans="1:12" ht="375">
@@ -17383,13 +17400,13 @@
         <v>1262</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>1774</v>
+        <v>1723</v>
       </c>
       <c r="F385" s="2" t="s">
-        <v>1766</v>
+        <v>1715</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>1767</v>
+        <v>1716</v>
       </c>
       <c r="J385" s="1" t="s">
         <v>18</v>
@@ -17409,13 +17426,13 @@
         <v>1262</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>1775</v>
+        <v>1724</v>
       </c>
       <c r="F386" s="2" t="s">
-        <v>1776</v>
+        <v>1725</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>1777</v>
+        <v>1726</v>
       </c>
       <c r="J386" s="1" t="s">
         <v>18</v>
@@ -17435,10 +17452,10 @@
         <v>1262</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>1778</v>
+        <v>1727</v>
       </c>
       <c r="F387" s="2" t="s">
-        <v>1779</v>
+        <v>1728</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>18</v>
@@ -17461,13 +17478,13 @@
         <v>1262</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>1780</v>
+        <v>1729</v>
       </c>
       <c r="F388" s="2" t="s">
-        <v>1781</v>
+        <v>1730</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>1882</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="389" spans="1:12" ht="30">
@@ -17484,13 +17501,13 @@
         <v>1262</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>1782</v>
+        <v>1731</v>
       </c>
       <c r="F389" s="2" t="s">
-        <v>1783</v>
+        <v>1732</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>1784</v>
+        <v>1733</v>
       </c>
       <c r="L389" s="1" t="s">
         <v>18</v>
@@ -17510,13 +17527,13 @@
         <v>1262</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>1785</v>
+        <v>1734</v>
       </c>
       <c r="F390" s="2" t="s">
-        <v>1786</v>
+        <v>1735</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>1787</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="60">
@@ -17533,13 +17550,13 @@
         <v>1262</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>1788</v>
+        <v>1737</v>
       </c>
       <c r="F391" s="2" t="s">
-        <v>1789</v>
+        <v>1738</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>1790</v>
+        <v>1739</v>
       </c>
       <c r="L391" s="1" t="s">
         <v>18</v>
@@ -17559,13 +17576,13 @@
         <v>1262</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>1791</v>
+        <v>1740</v>
       </c>
       <c r="F392" s="2" t="s">
-        <v>1792</v>
+        <v>1741</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>1793</v>
+        <v>1742</v>
       </c>
       <c r="J392" s="1" t="s">
         <v>18</v>
@@ -17585,10 +17602,10 @@
         <v>1262</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>1794</v>
+        <v>1743</v>
       </c>
       <c r="F393" s="2" t="s">
-        <v>1795</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="394" spans="1:12" ht="60">
@@ -17605,10 +17622,10 @@
         <v>1262</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>1796</v>
+        <v>1745</v>
       </c>
       <c r="F394" s="2" t="s">
-        <v>1797</v>
+        <v>1746</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>18</v>
@@ -17628,13 +17645,13 @@
         <v>1262</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>1798</v>
+        <v>1747</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>1799</v>
+        <v>1748</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>1800</v>
+        <v>1749</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>18</v>
@@ -17657,13 +17674,13 @@
         <v>1262</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>1801</v>
+        <v>1750</v>
       </c>
       <c r="F396" s="2" t="s">
-        <v>1802</v>
+        <v>1751</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>1922</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="397" spans="1:12" ht="105">
@@ -17680,13 +17697,13 @@
         <v>1262</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>1803</v>
+        <v>1752</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>1804</v>
+        <v>1753</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>1805</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="398" spans="1:12" ht="45">
@@ -17703,10 +17720,10 @@
         <v>1262</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>1806</v>
+        <v>1755</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>1807</v>
+        <v>1756</v>
       </c>
       <c r="L398" s="1" t="s">
         <v>18</v>
@@ -17720,19 +17737,19 @@
         <v>1343</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>1930</v>
+        <v>1879</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>1262</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>1808</v>
+        <v>1757</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>1809</v>
+        <v>1758</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>1810</v>
+        <v>1759</v>
       </c>
       <c r="L399" s="1" t="s">
         <v>18</v>
@@ -17752,13 +17769,13 @@
         <v>1262</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>1811</v>
+        <v>1760</v>
       </c>
       <c r="F400" s="2" t="s">
-        <v>1812</v>
+        <v>1761</v>
       </c>
       <c r="H400" s="2" t="s">
-        <v>1813</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="401" spans="1:12" ht="120">
@@ -17775,13 +17792,13 @@
         <v>1262</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>1814</v>
+        <v>1763</v>
       </c>
       <c r="F401" s="2" t="s">
-        <v>1815</v>
+        <v>1764</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>2034</v>
+        <v>1983</v>
       </c>
       <c r="J401" s="1" t="s">
         <v>18</v>
@@ -17801,10 +17818,10 @@
         <v>1262</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>1816</v>
+        <v>1765</v>
       </c>
       <c r="F402" s="2" t="s">
-        <v>1817</v>
+        <v>1766</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>18</v>
@@ -17827,13 +17844,13 @@
         <v>1262</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>1818</v>
+        <v>1767</v>
       </c>
       <c r="F403" s="2" t="s">
-        <v>1819</v>
+        <v>1768</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>1820</v>
+        <v>1769</v>
       </c>
       <c r="L403" s="1" t="s">
         <v>18</v>
@@ -17853,13 +17870,13 @@
         <v>1262</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>1821</v>
+        <v>1770</v>
       </c>
       <c r="F404" s="2" t="s">
-        <v>1822</v>
+        <v>1771</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>1805</v>
+        <v>1754</v>
       </c>
       <c r="J404" s="1" t="s">
         <v>18</v>
@@ -17879,13 +17896,13 @@
         <v>1262</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>1823</v>
+        <v>1772</v>
       </c>
       <c r="F405" s="2" t="s">
-        <v>1824</v>
+        <v>1773</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>2034</v>
+        <v>1983</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>18</v>
@@ -17905,10 +17922,10 @@
         <v>1262</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>1825</v>
+        <v>1774</v>
       </c>
       <c r="F406" s="2" t="s">
-        <v>1879</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="407" spans="1:12" ht="45">
@@ -17925,10 +17942,10 @@
         <v>1262</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>1826</v>
+        <v>1775</v>
       </c>
       <c r="F407" s="2" t="s">
-        <v>1827</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="408" spans="1:12" ht="30">
@@ -17945,10 +17962,10 @@
         <v>1262</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>1828</v>
+        <v>1777</v>
       </c>
       <c r="F408" s="2" t="s">
-        <v>1829</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="409" spans="1:12" ht="45">
@@ -17965,13 +17982,13 @@
         <v>1262</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>1830</v>
+        <v>1779</v>
       </c>
       <c r="F409" s="2" t="s">
-        <v>1831</v>
+        <v>1780</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>1832</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="410" spans="1:12" ht="90">
@@ -17988,13 +18005,13 @@
         <v>1262</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>1833</v>
+        <v>1782</v>
       </c>
       <c r="F410" s="2" t="s">
-        <v>1834</v>
+        <v>1783</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>1835</v>
+        <v>1784</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>18</v>
@@ -18017,13 +18034,13 @@
         <v>1262</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>1836</v>
+        <v>1785</v>
       </c>
       <c r="F411" s="2" t="s">
-        <v>1837</v>
+        <v>1786</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>1838</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="105">
@@ -18040,13 +18057,13 @@
         <v>1262</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>1839</v>
+        <v>1788</v>
       </c>
       <c r="F412" s="2" t="s">
-        <v>1840</v>
+        <v>1789</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>1777</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="413" spans="1:12" ht="135">
@@ -18063,13 +18080,13 @@
         <v>1262</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>1841</v>
+        <v>1790</v>
       </c>
       <c r="F413" s="2" t="s">
-        <v>1842</v>
+        <v>1791</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>1843</v>
+        <v>1792</v>
       </c>
       <c r="J413" s="1" t="s">
         <v>18</v>
@@ -18089,13 +18106,13 @@
         <v>1262</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>1844</v>
+        <v>1793</v>
       </c>
       <c r="F414" s="2" t="s">
-        <v>1878</v>
+        <v>1827</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>1880</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="415" spans="1:12" ht="225">
@@ -18112,13 +18129,13 @@
         <v>1262</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>1845</v>
+        <v>1794</v>
       </c>
       <c r="F415" s="2" t="s">
-        <v>1881</v>
+        <v>1830</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>1882</v>
+        <v>1831</v>
       </c>
       <c r="L415" s="1" t="s">
         <v>18</v>
@@ -18138,10 +18155,10 @@
         <v>1262</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>1846</v>
+        <v>1795</v>
       </c>
       <c r="F416" s="2" t="s">
-        <v>1883</v>
+        <v>1832</v>
       </c>
       <c r="L416" s="1" t="s">
         <v>18</v>
@@ -18161,10 +18178,10 @@
         <v>1262</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>1847</v>
+        <v>1796</v>
       </c>
       <c r="F417" s="2" t="s">
-        <v>1884</v>
+        <v>1833</v>
       </c>
       <c r="L417" s="1" t="s">
         <v>18</v>
@@ -18184,13 +18201,13 @@
         <v>1262</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>1848</v>
+        <v>1797</v>
       </c>
       <c r="F418" s="2" t="s">
-        <v>1885</v>
+        <v>1834</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>1800</v>
+        <v>1749</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>18</v>
@@ -18213,13 +18230,13 @@
         <v>1262</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>1849</v>
+        <v>1798</v>
       </c>
       <c r="F419" s="2" t="s">
-        <v>1886</v>
+        <v>1835</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>1914</v>
+        <v>1863</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>18</v>
@@ -18242,10 +18259,10 @@
         <v>1262</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>1850</v>
+        <v>1799</v>
       </c>
       <c r="F420" s="2" t="s">
-        <v>1887</v>
+        <v>1836</v>
       </c>
       <c r="J420" s="1" t="s">
         <v>18</v>
@@ -18265,13 +18282,13 @@
         <v>1262</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>1851</v>
+        <v>1800</v>
       </c>
       <c r="F421" s="2" t="s">
-        <v>1888</v>
+        <v>1837</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>2035</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="422" spans="1:12" ht="45">
@@ -18288,13 +18305,13 @@
         <v>1262</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>1852</v>
+        <v>1801</v>
       </c>
       <c r="F422" s="2" t="s">
-        <v>1889</v>
+        <v>1838</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>1915</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="423" spans="1:12" ht="60">
@@ -18311,10 +18328,10 @@
         <v>1262</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>1853</v>
+        <v>1802</v>
       </c>
       <c r="F423" s="2" t="s">
-        <v>1890</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="424" spans="1:12" ht="330">
@@ -18331,13 +18348,13 @@
         <v>1262</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>1854</v>
+        <v>1803</v>
       </c>
       <c r="F424" s="2" t="s">
-        <v>1891</v>
+        <v>1840</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>2051</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="425" spans="1:12" ht="45">
@@ -18354,10 +18371,10 @@
         <v>1262</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>1855</v>
+        <v>1804</v>
       </c>
       <c r="F425" s="2" t="s">
-        <v>1892</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="426" spans="1:12" ht="45">
@@ -18374,13 +18391,13 @@
         <v>1262</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>1856</v>
+        <v>1805</v>
       </c>
       <c r="F426" s="2" t="s">
-        <v>1893</v>
+        <v>1842</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>1832</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="427" spans="1:12" ht="30">
@@ -18397,10 +18414,10 @@
         <v>1262</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>1857</v>
+        <v>1806</v>
       </c>
       <c r="F427" s="2" t="s">
-        <v>1894</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="428" spans="1:12" ht="45">
@@ -18417,10 +18434,10 @@
         <v>1262</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>1858</v>
+        <v>1807</v>
       </c>
       <c r="F428" s="2" t="s">
-        <v>1895</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="429" spans="1:12" ht="30">
@@ -18437,10 +18454,10 @@
         <v>1262</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>1859</v>
+        <v>1808</v>
       </c>
       <c r="F429" s="2" t="s">
-        <v>1896</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="430" spans="1:12" ht="45">
@@ -18457,13 +18474,13 @@
         <v>1262</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>1860</v>
+        <v>1809</v>
       </c>
       <c r="F430" s="2" t="s">
-        <v>1897</v>
+        <v>1846</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>1916</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="431" spans="1:12" ht="45">
@@ -18480,13 +18497,13 @@
         <v>1262</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>1861</v>
+        <v>1810</v>
       </c>
       <c r="F431" s="2" t="s">
-        <v>1898</v>
+        <v>1847</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>1917</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="432" spans="1:12" ht="225">
@@ -18503,13 +18520,13 @@
         <v>1262</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>1862</v>
+        <v>1811</v>
       </c>
       <c r="F432" s="2" t="s">
-        <v>1754</v>
+        <v>1703</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>2036</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="433" spans="1:12" ht="120">
@@ -18526,13 +18543,13 @@
         <v>1262</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>1863</v>
+        <v>1812</v>
       </c>
       <c r="F433" s="2" t="s">
-        <v>1899</v>
+        <v>1848</v>
       </c>
       <c r="H433" s="2" t="s">
-        <v>1729</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="434" spans="1:12" ht="120">
@@ -18549,13 +18566,13 @@
         <v>1262</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>1864</v>
+        <v>1813</v>
       </c>
       <c r="F434" s="2" t="s">
-        <v>1900</v>
+        <v>1849</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>2034</v>
+        <v>1983</v>
       </c>
       <c r="J434" s="1" t="s">
         <v>18</v>
@@ -18578,13 +18595,13 @@
         <v>1262</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>1865</v>
+        <v>1814</v>
       </c>
       <c r="F435" s="2" t="s">
-        <v>1901</v>
+        <v>1850</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>2035</v>
+        <v>1984</v>
       </c>
       <c r="J435" s="1" t="s">
         <v>18</v>
@@ -18604,13 +18621,13 @@
         <v>1262</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>1866</v>
+        <v>1815</v>
       </c>
       <c r="F436" s="2" t="s">
-        <v>1902</v>
+        <v>1851</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>1918</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="437" spans="1:12" ht="45">
@@ -18627,13 +18644,13 @@
         <v>1262</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>1867</v>
+        <v>1816</v>
       </c>
       <c r="F437" s="2" t="s">
-        <v>1903</v>
+        <v>1852</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>1919</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="438" spans="1:12" ht="75">
@@ -18650,13 +18667,13 @@
         <v>1262</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>1868</v>
+        <v>1817</v>
       </c>
       <c r="F438" s="2" t="s">
-        <v>1932</v>
+        <v>1881</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>1920</v>
+        <v>1869</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>18</v>
@@ -18679,13 +18696,13 @@
         <v>1262</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>1869</v>
+        <v>1818</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>1904</v>
+        <v>1853</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>1921</v>
+        <v>1870</v>
       </c>
       <c r="L439" s="1" t="s">
         <v>18</v>
@@ -18705,13 +18722,13 @@
         <v>1262</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>1870</v>
+        <v>1819</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>1905</v>
+        <v>1854</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>2031</v>
+        <v>1980</v>
       </c>
       <c r="L440" s="1" t="s">
         <v>18</v>
@@ -18731,13 +18748,13 @@
         <v>1262</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>1871</v>
+        <v>1820</v>
       </c>
       <c r="F441" s="2" t="s">
-        <v>1906</v>
+        <v>1855</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>1762</v>
+        <v>1711</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>18</v>
@@ -18760,13 +18777,13 @@
         <v>1262</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>1872</v>
+        <v>1821</v>
       </c>
       <c r="F442" s="2" t="s">
-        <v>1907</v>
+        <v>1856</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>1922</v>
+        <v>1871</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>18</v>
@@ -18789,13 +18806,13 @@
         <v>1262</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>1873</v>
+        <v>1822</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>1908</v>
+        <v>1857</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>1923</v>
+        <v>1872</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>18</v>
@@ -18818,13 +18835,13 @@
         <v>1262</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>1874</v>
+        <v>1823</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>1909</v>
+        <v>1858</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>1882</v>
+        <v>1831</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>18</v>
@@ -18847,13 +18864,13 @@
         <v>1262</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>1875</v>
+        <v>1824</v>
       </c>
       <c r="F445" s="2" t="s">
-        <v>1910</v>
+        <v>1859</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>1922</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="446" spans="1:12" ht="60">
@@ -18870,13 +18887,13 @@
         <v>1262</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>1876</v>
+        <v>1825</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>1911</v>
+        <v>1860</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>2032</v>
+        <v>1981</v>
       </c>
       <c r="J446" s="1" t="s">
         <v>18</v>
@@ -18896,13 +18913,13 @@
         <v>1262</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>1877</v>
+        <v>1826</v>
       </c>
       <c r="F447" s="2" t="s">
-        <v>1912</v>
+        <v>1861</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>1924</v>
+        <v>1873</v>
       </c>
     </row>
   </sheetData>
@@ -19799,7 +19816,7 @@
         <v>1598</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>1599</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="15.75">
@@ -19807,19 +19824,19 @@
         <v>1040</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>1601</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>1602</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75">
@@ -19827,22 +19844,22 @@
         <v>1041</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D42" s="1" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>1605</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>1606</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>1607</v>
-      </c>
       <c r="G42" s="13" t="s">
-        <v>1608</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="15.75">
@@ -19850,22 +19867,22 @@
         <v>1042</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>1611</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>1612</v>
-      </c>
       <c r="G43" s="13" t="s">
-        <v>1613</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.75">
@@ -19873,22 +19890,22 @@
         <v>1043</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>1608</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="15.75">
@@ -19896,22 +19913,22 @@
         <v>1044</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>1613</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75">
@@ -19919,22 +19936,22 @@
         <v>1045</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>1623</v>
+        <v>2007</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="15.75">
@@ -19942,25 +19959,25 @@
         <v>1046</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>1629</v>
+        <v>1469</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="15.75">
@@ -19968,22 +19985,22 @@
         <v>1047</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>1632</v>
+        <v>1627</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>1608</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75">
@@ -19991,22 +20008,22 @@
         <v>1048</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>1636</v>
+        <v>1631</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>1613</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75">
@@ -20014,19 +20031,19 @@
         <v>1049</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>1640</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.75">
@@ -20034,16 +20051,16 @@
         <v>1050</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>1641</v>
+        <v>1635</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>1642</v>
+        <v>1636</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1643</v>
+        <v>1637</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>1570</v>
@@ -20054,16 +20071,16 @@
         <v>1051</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>1644</v>
+        <v>1638</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>1262</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>1913</v>
+        <v>1862</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>1645</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.75">
@@ -20117,15 +20134,15 @@
         <v>1441</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75">
       <c r="A2">
         <v>2000</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>1647</v>
+      <c r="B2" s="21" t="s">
+        <v>2010</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>13</v>
@@ -20137,8 +20154,8 @@
       <c r="A3">
         <v>2001</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>1648</v>
+      <c r="B3" s="21" t="s">
+        <v>2011</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>13</v>
@@ -20150,8 +20167,8 @@
       <c r="A4">
         <v>2002</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>1649</v>
+      <c r="B4" s="21" t="s">
+        <v>2012</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>13</v>
@@ -20163,8 +20180,8 @@
       <c r="A5">
         <v>2013</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>1650</v>
+      <c r="B5" s="21" t="s">
+        <v>2013</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>13</v>
@@ -20176,8 +20193,8 @@
       <c r="A6">
         <v>2014</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>1651</v>
+      <c r="B6" s="21" t="s">
+        <v>2014</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>13</v>
@@ -20189,8 +20206,8 @@
       <c r="A7">
         <v>2017</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>1652</v>
+      <c r="B7" s="21" t="s">
+        <v>2015</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>13</v>
@@ -20202,8 +20219,8 @@
       <c r="A8">
         <v>2010</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>1653</v>
+      <c r="B8" s="21" t="s">
+        <v>2016</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>13</v>
@@ -20215,8 +20232,8 @@
       <c r="A9">
         <v>2008</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>1654</v>
+      <c r="B9" s="21" t="s">
+        <v>2017</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>13</v>
@@ -20228,8 +20245,8 @@
       <c r="A10">
         <v>2021</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>1655</v>
+      <c r="B10" s="21" t="s">
+        <v>2018</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>13</v>
@@ -20241,8 +20258,8 @@
       <c r="A11">
         <v>2022</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>1656</v>
+      <c r="B11" s="21" t="s">
+        <v>2019</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>13</v>
@@ -20254,8 +20271,8 @@
       <c r="A12">
         <v>2012</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>1657</v>
+      <c r="B12" s="21" t="s">
+        <v>2020</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>13</v>
@@ -20267,8 +20284,8 @@
       <c r="A13">
         <v>2011</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>1658</v>
+      <c r="B13" s="21" t="s">
+        <v>2021</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>13</v>
@@ -20280,8 +20297,8 @@
       <c r="A14">
         <v>2015</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>1659</v>
+      <c r="B14" s="21" t="s">
+        <v>2022</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>13</v>
@@ -20293,8 +20310,8 @@
       <c r="A15">
         <v>2016</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>1660</v>
+      <c r="B15" s="21" t="s">
+        <v>2023</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>13</v>
@@ -20306,8 +20323,8 @@
       <c r="A16">
         <v>2023</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>1661</v>
+      <c r="B16" s="21" t="s">
+        <v>2024</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>13</v>
@@ -20319,8 +20336,8 @@
       <c r="A17">
         <v>2024</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>1662</v>
+      <c r="B17" s="21" t="s">
+        <v>2025</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>13</v>
@@ -20332,8 +20349,8 @@
       <c r="A18">
         <v>2020</v>
       </c>
-      <c r="B18" s="14" t="s">
-        <v>1663</v>
+      <c r="B18" s="21" t="s">
+        <v>2026</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>84</v>
@@ -20345,8 +20362,8 @@
       <c r="A19">
         <v>2003</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>1664</v>
+      <c r="B19" s="21" t="s">
+        <v>1641</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>84</v>
@@ -20358,8 +20375,8 @@
       <c r="A20">
         <v>2004</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>1665</v>
+      <c r="B20" s="21" t="s">
+        <v>2027</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>84</v>
@@ -20371,8 +20388,8 @@
       <c r="A21">
         <v>2006</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>1666</v>
+      <c r="B21" s="21" t="s">
+        <v>2028</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>84</v>
@@ -20384,8 +20401,8 @@
       <c r="A22">
         <v>2005</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>1667</v>
+      <c r="B22" s="21" t="s">
+        <v>2029</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>84</v>
@@ -20397,8 +20414,8 @@
       <c r="A23">
         <v>2018</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>1668</v>
+      <c r="B23" s="21" t="s">
+        <v>2030</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>84</v>
@@ -20410,8 +20427,8 @@
       <c r="A24">
         <v>2009</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>1669</v>
+      <c r="B24" s="21" t="s">
+        <v>2031</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>84</v>
@@ -20423,8 +20440,8 @@
       <c r="A25">
         <v>2025</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>1670</v>
+      <c r="B25" s="21" t="s">
+        <v>2032</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>84</v>
@@ -20436,8 +20453,8 @@
       <c r="A26">
         <v>2007</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>1671</v>
+      <c r="B26" s="21" t="s">
+        <v>2033</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>84</v>
@@ -20449,8 +20466,8 @@
       <c r="A27">
         <v>2019</v>
       </c>
-      <c r="B27" s="14" t="s">
-        <v>1672</v>
+      <c r="B27" s="21" t="s">
+        <v>2034</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>84</v>
@@ -20461,8 +20478,8 @@
       <c r="A28">
         <v>2031</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>1673</v>
+      <c r="B28" s="21" t="s">
+        <v>2035</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>958</v>
@@ -20474,8 +20491,8 @@
       <c r="A29">
         <v>2030</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>1674</v>
+      <c r="B29" s="21" t="s">
+        <v>2036</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>958</v>
@@ -20487,8 +20504,8 @@
       <c r="A30">
         <v>2033</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>1675</v>
+      <c r="B30" s="21" t="s">
+        <v>2037</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>958</v>
@@ -20500,8 +20517,8 @@
       <c r="A31">
         <v>2032</v>
       </c>
-      <c r="B31" s="14" t="s">
-        <v>1676</v>
+      <c r="B31" s="21" t="s">
+        <v>2038</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>958</v>
@@ -20512,8 +20529,8 @@
       <c r="A32">
         <v>2026</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>1677</v>
+      <c r="B32" s="21" t="s">
+        <v>2039</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>958</v>
@@ -20525,8 +20542,8 @@
       <c r="A33">
         <v>2027</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>1678</v>
+      <c r="B33" s="21" t="s">
+        <v>2040</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>958</v>
@@ -20538,8 +20555,8 @@
       <c r="A34">
         <v>2029</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>1679</v>
+      <c r="B34" s="21" t="s">
+        <v>2041</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>958</v>
@@ -20551,8 +20568,8 @@
       <c r="A35">
         <v>2028</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>1680</v>
+      <c r="B35" s="21" t="s">
+        <v>2042</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>958</v>
@@ -20564,8 +20581,8 @@
       <c r="A36">
         <v>2043</v>
       </c>
-      <c r="B36" s="14" t="s">
-        <v>1681</v>
+      <c r="B36" s="22" t="s">
+        <v>2043</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>1262</v>
@@ -20578,8 +20595,8 @@
       <c r="A37">
         <v>2040</v>
       </c>
-      <c r="B37" s="14" t="s">
-        <v>1682</v>
+      <c r="B37" s="21" t="s">
+        <v>2044</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>1262</v>
@@ -20592,8 +20609,8 @@
       <c r="A38">
         <v>2035</v>
       </c>
-      <c r="B38" s="14" t="s">
-        <v>1683</v>
+      <c r="B38" s="21" t="s">
+        <v>2045</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>1262</v>
@@ -20606,8 +20623,8 @@
       <c r="A39">
         <v>2041</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>1684</v>
+      <c r="B39" s="21" t="s">
+        <v>2046</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>1262</v>
@@ -20620,8 +20637,8 @@
       <c r="A40">
         <v>2042</v>
       </c>
-      <c r="B40" s="14" t="s">
-        <v>1685</v>
+      <c r="B40" s="21" t="s">
+        <v>2047</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>1262</v>
@@ -20634,8 +20651,8 @@
       <c r="A41">
         <v>2044</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>1686</v>
+      <c r="B41" s="21" t="s">
+        <v>2048</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>1262</v>
@@ -20648,8 +20665,8 @@
       <c r="A42">
         <v>2036</v>
       </c>
-      <c r="B42" s="14" t="s">
-        <v>1687</v>
+      <c r="B42" s="21" t="s">
+        <v>2049</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>1262</v>
@@ -20662,8 +20679,8 @@
       <c r="A43">
         <v>2034</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>1688</v>
+      <c r="B43" s="21" t="s">
+        <v>2050</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>1262</v>
@@ -20676,8 +20693,8 @@
       <c r="A44">
         <v>2037</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>1689</v>
+      <c r="B44" s="21" t="s">
+        <v>2051</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>1262</v>
@@ -20690,8 +20707,8 @@
       <c r="A45">
         <v>2038</v>
       </c>
-      <c r="B45" s="14" t="s">
-        <v>1690</v>
+      <c r="B45" s="21" t="s">
+        <v>2052</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>1262</v>
@@ -20704,8 +20721,8 @@
       <c r="A46">
         <v>2039</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>1691</v>
+      <c r="B46" s="21" t="s">
+        <v>2053</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>1262</v>
@@ -20718,8 +20735,8 @@
       <c r="A47">
         <v>2045</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>1692</v>
+      <c r="B47" s="21" t="s">
+        <v>2054</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>1262</v>
@@ -20754,55 +20771,55 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1693</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>1694</v>
+        <v>1643</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1695</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>1696</v>
+        <v>1645</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1697</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>1698</v>
+        <v>1647</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1699</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>1700</v>
+        <v>1649</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1701</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>1702</v>
+        <v>1651</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1703</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>1704</v>
+        <v>1653</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1705</v>
+        <v>1654</v>
       </c>
     </row>
   </sheetData>
@@ -20831,12 +20848,12 @@
         <v>1440</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>1706</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1707</v>
+        <v>1656</v>
       </c>
       <c r="B2" t="b">
         <f>FALSE()</f>
